--- a/datasets/Strategic-Sales-Operations-Performamce Dashboard.xlsx
+++ b/datasets/Strategic-Sales-Operations-Performamce Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\my data analytics projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D12CA52-BFFD-4B29-B654-1862CF9A98C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06639DAC-0D6A-48D7-8B41-358DB60444FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.1 Region-Wise Product Sales" sheetId="18" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="388">
   <si>
     <t>Product ID</t>
   </si>
@@ -1067,13 +1067,7 @@
     <t>NO</t>
   </si>
   <si>
-    <t>Fast</t>
-  </si>
-  <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>Slow</t>
   </si>
   <si>
     <t>PRODUCT NAME</t>
@@ -1164,37 +1158,10 @@
     <t>Ans: Highest-Selling product by Revenue is Smartphone .</t>
   </si>
   <si>
-    <t>Jan</t>
-  </si>
-  <si>
-    <t>Feb</t>
-  </si>
-  <si>
     <t>Mar</t>
   </si>
   <si>
-    <t>Apr</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Jun</t>
-  </si>
-  <si>
-    <t>Jul</t>
-  </si>
-  <si>
-    <t>Aug</t>
-  </si>
-  <si>
-    <t>Sep</t>
-  </si>
-  <si>
     <t>Oct</t>
-  </si>
-  <si>
-    <t>Nov</t>
   </si>
   <si>
     <t>Dec</t>
@@ -1494,7 +1461,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1557,11 +1524,72 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="42">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -2343,7 +2371,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Books</c:v>
+                  <c:v>Home</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2351,7 +2379,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent5">
-                <a:shade val="53000"/>
+                <a:shade val="76000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -2420,47 +2448,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$10</c:f>
+              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$B$5:$B$10</c:f>
+              <c:f>'2.1 Region-Wise Product Sales'!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>84</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>394</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>464</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>423</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>350</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2480,279 +2484,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Electronics</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:shade val="76000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:sp3d/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$10</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$C$5:$C$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2662</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>365</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6522</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3938</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1722</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000005B-CDB9-4633-B146-6B01517ECCAE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$D$3:$D$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Fashion</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:sp3d/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$10</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$D$5:$D$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>210</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>711</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>788</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1032</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1131</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000005C-CDB9-4633-B146-6B01517ECCAE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$E$3:$E$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Home</c:v>
+                  <c:v>Toys</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2829,191 +2561,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$10</c:f>
+              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$E$5:$E$10</c:f>
+              <c:f>'2.1 Region-Wise Product Sales'!$C$5:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2063</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>741</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2131</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1881</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4135</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000005D-CDB9-4633-B146-6B01517ECCAE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$F$3:$F$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Toys</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:tint val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:sp3d/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$10</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$F$5:$F$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>437</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1424</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>586</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1021</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000005E-CDB9-4633-B146-6B01517ECCAE}"/>
+              <c16:uniqueId val="{0000005B-CDB9-4633-B146-6B01517ECCAE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3422,7 +2993,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="92D050"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -3442,7 +3013,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFC000"/>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -3517,16 +3088,13 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'2.2Orders by Delivery status'!$A$4:$A$7</c:f>
+              <c:f>'2.2Orders by Delivery status'!$A$4:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>Cancelled</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Delivered</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>In Transit</c:v>
                 </c:pt>
               </c:strCache>
@@ -3534,18 +3102,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2.2Orders by Delivery status'!$B$4:$B$7</c:f>
+              <c:f>'2.2Orders by Delivery status'!$B$4:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>30</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>36</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3912,47 +3477,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'2.3Regional Average Delivery Ti'!$A$5:$A$10</c:f>
+              <c:f>'2.3Regional Average Delivery Ti'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2.3Regional Average Delivery Ti'!$B$5:$B$10</c:f>
+              <c:f>'2.3Regional Average Delivery Ti'!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4.2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.25</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.625</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.3333333333333335</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.4285714285714284</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4371,43 +3912,16 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'5.3Monthly Sales Trend'!$A$4:$A$16</c:f>
+              <c:f>'5.3Monthly Sales Trend'!$A$4:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Jan</c:v>
+                  <c:v>Mar</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Feb</c:v>
+                  <c:v>Oct</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Apr</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>May</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Jun</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Jul</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Aug</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Sep</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Oct</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Nov</c:v>
-                </c:pt>
-                <c:pt idx="11">
                   <c:v>Dec</c:v>
                 </c:pt>
               </c:strCache>
@@ -4415,45 +3929,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'5.3Monthly Sales Trend'!$B$4:$B$16</c:f>
+              <c:f>'5.3Monthly Sales Trend'!$B$4:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1099</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3712</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>905</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2637</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4940</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2599</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3315</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>782</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1570</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2920</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6312</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4467</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4878,13 +4365,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>10491</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8359</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7317</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>#N/A</c:v>
@@ -5010,19 +4497,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>145</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>145</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>#N/A</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5456</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3635</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6233,7 +5720,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Books</c:v>
+                  <c:v>Home</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6241,7 +5728,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent5">
-                <a:shade val="53000"/>
+                <a:shade val="76000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -6310,47 +5797,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$10</c:f>
+              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$B$5:$B$10</c:f>
+              <c:f>'2.1 Region-Wise Product Sales'!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>84</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>394</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>464</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>423</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>350</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6370,279 +5833,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Electronics</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:shade val="76000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:sp3d/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$10</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$C$5:$C$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2662</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>365</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6522</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3938</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1722</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000005B-0241-47FB-BAA3-52A378D53DF3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$D$3:$D$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Fashion</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:sp3d/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$10</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$D$5:$D$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>210</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>711</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>788</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1032</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1131</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000005C-0241-47FB-BAA3-52A378D53DF3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$E$3:$E$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Home</c:v>
+                  <c:v>Toys</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6719,191 +5910,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$10</c:f>
+              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$E$5:$E$10</c:f>
+              <c:f>'2.1 Region-Wise Product Sales'!$C$5:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2063</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>741</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2131</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1881</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4135</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000005D-0241-47FB-BAA3-52A378D53DF3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$F$3:$F$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Toys</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:tint val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:sp3d/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$A$5:$A$10</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'2.1 Region-Wise Product Sales'!$F$5:$F$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>437</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1424</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>586</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1021</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000005E-0241-47FB-BAA3-52A378D53DF3}"/>
+              <c16:uniqueId val="{0000005B-0241-47FB-BAA3-52A378D53DF3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7454,43 +6484,16 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'5.3Monthly Sales Trend'!$A$4:$A$16</c:f>
+              <c:f>'5.3Monthly Sales Trend'!$A$4:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Jan</c:v>
+                  <c:v>Mar</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Feb</c:v>
+                  <c:v>Oct</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Apr</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>May</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Jun</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Jul</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Aug</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Sep</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Oct</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Nov</c:v>
-                </c:pt>
-                <c:pt idx="11">
                   <c:v>Dec</c:v>
                 </c:pt>
               </c:strCache>
@@ -7498,45 +6501,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'5.3Monthly Sales Trend'!$B$4:$B$16</c:f>
+              <c:f>'5.3Monthly Sales Trend'!$B$4:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1099</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3712</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>905</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2637</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4940</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2599</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3315</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>782</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1570</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2920</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6312</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4467</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8101,47 +7077,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'2.3Regional Average Delivery Ti'!$A$5:$A$10</c:f>
+              <c:f>'2.3Regional Average Delivery Ti'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2.3Regional Average Delivery Ti'!$B$5:$B$10</c:f>
+              <c:f>'2.3Regional Average Delivery Ti'!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4.2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.25</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.625</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.3333333333333335</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.4285714285714284</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8763,7 +7715,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="92D050"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -8783,7 +7735,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFC000"/>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -8858,16 +7810,13 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'2.2Orders by Delivery status'!$A$4:$A$7</c:f>
+              <c:f>'2.2Orders by Delivery status'!$A$4:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>Cancelled</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Delivered</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>In Transit</c:v>
                 </c:pt>
               </c:strCache>
@@ -8875,18 +7824,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2.2Orders by Delivery status'!$B$4:$B$7</c:f>
+              <c:f>'2.2Orders by Delivery status'!$B$4:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>30</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>36</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14275,9 +13221,9 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t>Central-5456
-East-3635
-North-10491</a:t>
+            <a:t>North-145
+Grand Total-145
+-</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2000"/>
         </a:p>
@@ -14725,7 +13671,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t>% Fast Delivery --0.323529411764706</a:t>
+            <a:t>% Fast Delivery --1</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1600">
             <a:solidFill>
@@ -14801,7 +13747,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t>Total Revnue-35258</a:t>
+            <a:t>Total Revnue-145</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1800"/>
         </a:p>
@@ -14874,7 +13820,7 @@
             </a:rPr>
             <a:pPr algn="l"/>
             <a:t>Highest Selling Produsts by Units
-Leg Set-8</a:t>
+Lamp-1</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1600"/>
         </a:p>
@@ -14947,7 +13893,7 @@
             </a:rPr>
             <a:pPr algn="l"/>
             <a:t>Highest-Selling product by Revenue
-Smartphone-9644</a:t>
+Leg Set-64</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1600"/>
         </a:p>
@@ -17962,18 +16908,18 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CA633477-BD8F-43E5-AC6D-C963095F53A4}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
-  <location ref="A3:G10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <location ref="A3:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -17982,11 +16928,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18206,21 +17152,9 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -18229,16 +17163,7 @@
   <colFields count="1">
     <field x="14"/>
   </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
+  <colItems count="3">
     <i>
       <x v="3"/>
     </i>
@@ -18406,18 +17331,18 @@
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D63542FF-3718-481A-811A-875F981A7DCC}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18426,11 +17351,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18650,39 +17575,12 @@
     <field x="19"/>
     <field x="10"/>
   </rowFields>
-  <rowItems count="13">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
+  <rowItems count="4">
     <i>
       <x v="3"/>
     </i>
     <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
       <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
     </i>
     <i>
       <x v="12"/>
@@ -18731,18 +17629,18 @@
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E40B2FD2-3CB9-4A84-A10D-24508FDBC3A1}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -18760,11 +17658,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18983,21 +17881,9 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="2">
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -19644,7 +18530,7 @@
     <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="15">
+    <format dxfId="35">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -20331,7 +19217,7 @@
     <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="19">
+    <format dxfId="39">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="14" count="1" selected="0">
@@ -20343,7 +19229,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="14" count="1" selected="0">
@@ -20355,7 +19241,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="14" count="1">
@@ -20364,7 +19250,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="14" count="1">
@@ -20648,304 +19534,19 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7AD66EF4-25E2-4CDC-BCB8-079B388A220D}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="X109:AB111" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="23">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="82">
-        <item x="52"/>
-        <item x="25"/>
-        <item x="63"/>
-        <item x="49"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="48"/>
-        <item x="15"/>
-        <item x="28"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="1"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="50"/>
-        <item x="61"/>
-        <item x="29"/>
-        <item x="80"/>
-        <item x="7"/>
-        <item x="54"/>
-        <item x="19"/>
-        <item x="57"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="53"/>
-        <item x="47"/>
-        <item x="58"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="23"/>
-        <item x="76"/>
-        <item x="43"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="16"/>
-        <item x="60"/>
-        <item x="77"/>
-        <item x="71"/>
-        <item x="40"/>
-        <item x="45"/>
-        <item x="8"/>
-        <item x="62"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item x="59"/>
-        <item x="6"/>
-        <item x="36"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="65"/>
-        <item x="55"/>
-        <item x="39"/>
-        <item x="79"/>
-        <item x="20"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="2"/>
-        <item x="24"/>
-        <item x="67"/>
-        <item x="35"/>
-        <item x="51"/>
-        <item x="46"/>
-        <item x="69"/>
-        <item x="5"/>
-        <item x="22"/>
-        <item x="68"/>
-        <item x="21"/>
-        <item x="70"/>
-        <item x="32"/>
-        <item x="56"/>
-        <item x="17"/>
-        <item x="37"/>
-        <item x="66"/>
-        <item x="44"/>
-        <item x="75"/>
-        <item x="42"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="38"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="33">
-        <item x="19"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="18"/>
-        <item x="15"/>
-        <item x="30"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="29"/>
-        <item x="3"/>
-        <item x="31"/>
-        <item x="11"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="25"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="28"/>
-        <item x="26"/>
-        <item x="4"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="23"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2990033C-D272-4515-AFC8-96BC4B8D49ED}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="CM36:CN39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CBE17960-FE76-46FF-AA6D-9E5422A84361}" name="PivotTable18" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="BG24:BH28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -20954,11 +19555,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -21204,322 +19805,15 @@
   <rowFields count="1">
     <field x="18"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="4">
+    <i>
+      <x v="10"/>
+    </i>
     <i>
       <x v="11"/>
     </i>
     <i>
-      <x v="19"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Total Amount" fld="6" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="18" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="1" filterVal="1"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CBE17960-FE76-46FF-AA6D-9E5422A84361}" name="PivotTable18" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="BG24:BH27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="23">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="82">
-        <item x="52"/>
-        <item x="25"/>
-        <item x="63"/>
-        <item x="49"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="48"/>
-        <item x="15"/>
-        <item x="28"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="1"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="50"/>
-        <item x="61"/>
-        <item x="29"/>
-        <item x="80"/>
-        <item x="7"/>
-        <item x="54"/>
-        <item x="19"/>
-        <item x="57"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="53"/>
-        <item x="47"/>
-        <item x="58"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="23"/>
-        <item x="76"/>
-        <item x="43"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="16"/>
-        <item x="60"/>
-        <item x="77"/>
-        <item x="71"/>
-        <item x="40"/>
-        <item x="45"/>
-        <item x="8"/>
-        <item x="62"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item x="59"/>
-        <item x="6"/>
-        <item x="36"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="65"/>
-        <item x="55"/>
-        <item x="39"/>
-        <item x="79"/>
-        <item x="20"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="2"/>
-        <item x="24"/>
-        <item x="67"/>
-        <item x="35"/>
-        <item x="51"/>
-        <item x="46"/>
-        <item x="69"/>
-        <item x="5"/>
-        <item x="22"/>
-        <item x="68"/>
-        <item x="21"/>
-        <item x="70"/>
-        <item x="32"/>
-        <item x="56"/>
-        <item x="17"/>
-        <item x="37"/>
-        <item x="66"/>
-        <item x="44"/>
-        <item x="75"/>
-        <item x="42"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="38"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="33">
-        <item x="19"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="18"/>
-        <item x="15"/>
-        <item x="30"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="29"/>
-        <item x="3"/>
-        <item x="31"/>
-        <item x="11"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="25"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="28"/>
-        <item x="26"/>
-        <item x="4"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="23"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="23">
-        <item x="15"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="19"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="18"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="12"/>
-        <item x="20"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="8"/>
-        <item x="13"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="18"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="19"/>
+      <x v="21"/>
     </i>
     <i t="grand">
       <x/>
@@ -21552,675 +19846,20 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E30E125-2571-4287-88E1-5AFA8E91D3A7}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{839F4447-4F37-46E9-85EE-A9A4A65BA018}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="AE110:AE111" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="23">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="82">
-        <item x="52"/>
-        <item x="25"/>
-        <item x="63"/>
-        <item x="49"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="48"/>
-        <item x="15"/>
-        <item x="28"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="1"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="50"/>
-        <item x="61"/>
-        <item x="29"/>
-        <item x="80"/>
-        <item x="7"/>
-        <item x="54"/>
-        <item x="19"/>
-        <item x="57"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="53"/>
-        <item x="47"/>
-        <item x="58"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="23"/>
-        <item x="76"/>
-        <item x="43"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="16"/>
-        <item x="60"/>
-        <item x="77"/>
-        <item x="71"/>
-        <item x="40"/>
-        <item x="45"/>
-        <item x="8"/>
-        <item x="62"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item x="59"/>
-        <item x="6"/>
-        <item x="36"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="65"/>
-        <item x="55"/>
-        <item x="39"/>
-        <item x="79"/>
-        <item x="20"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="2"/>
-        <item x="24"/>
-        <item x="67"/>
-        <item x="35"/>
-        <item x="51"/>
-        <item x="46"/>
-        <item x="69"/>
-        <item x="5"/>
-        <item x="22"/>
-        <item x="68"/>
-        <item x="21"/>
-        <item x="70"/>
-        <item x="32"/>
-        <item x="56"/>
-        <item x="17"/>
-        <item x="37"/>
-        <item x="66"/>
-        <item x="44"/>
-        <item x="75"/>
-        <item x="42"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="38"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="33">
-        <item x="19"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="18"/>
-        <item x="15"/>
-        <item x="30"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="29"/>
-        <item x="3"/>
-        <item x="31"/>
-        <item x="11"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="25"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="28"/>
-        <item x="26"/>
-        <item x="4"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="23"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="13" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="33" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="33" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="33" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="33" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{22C8BE52-12B2-49F3-829B-86C223E7AEBF}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="BP34:BT36" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="23">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="82">
-        <item x="52"/>
-        <item x="25"/>
-        <item x="63"/>
-        <item x="49"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="48"/>
-        <item x="15"/>
-        <item x="28"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="1"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="50"/>
-        <item x="61"/>
-        <item x="29"/>
-        <item x="80"/>
-        <item x="7"/>
-        <item x="54"/>
-        <item x="19"/>
-        <item x="57"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="53"/>
-        <item x="47"/>
-        <item x="58"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="23"/>
-        <item x="76"/>
-        <item x="43"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="16"/>
-        <item x="60"/>
-        <item x="77"/>
-        <item x="71"/>
-        <item x="40"/>
-        <item x="45"/>
-        <item x="8"/>
-        <item x="62"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item x="59"/>
-        <item x="6"/>
-        <item x="36"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="65"/>
-        <item x="55"/>
-        <item x="39"/>
-        <item x="79"/>
-        <item x="20"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="2"/>
-        <item x="24"/>
-        <item x="67"/>
-        <item x="35"/>
-        <item x="51"/>
-        <item x="46"/>
-        <item x="69"/>
-        <item x="5"/>
-        <item x="22"/>
-        <item x="68"/>
-        <item x="21"/>
-        <item x="70"/>
-        <item x="32"/>
-        <item x="56"/>
-        <item x="17"/>
-        <item x="37"/>
-        <item x="66"/>
-        <item x="44"/>
-        <item x="75"/>
-        <item x="42"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="38"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="33">
-        <item x="19"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="18"/>
-        <item x="15"/>
-        <item x="30"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="29"/>
-        <item x="3"/>
-        <item x="31"/>
-        <item x="11"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="25"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="28"/>
-        <item x="26"/>
-        <item x="4"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="23"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable21.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1D668290-96DF-4F7E-8FE1-3AAB3593B7DF}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="">
-  <location ref="CF24:CG30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="23">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -22229,1001 +19868,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="82">
-        <item x="52"/>
-        <item x="25"/>
-        <item x="63"/>
-        <item x="49"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="48"/>
-        <item x="15"/>
-        <item x="28"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="1"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="50"/>
-        <item x="61"/>
-        <item x="29"/>
-        <item x="80"/>
-        <item x="7"/>
-        <item x="54"/>
-        <item x="19"/>
-        <item x="57"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="53"/>
-        <item x="47"/>
-        <item x="58"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="23"/>
-        <item x="76"/>
-        <item x="43"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="16"/>
-        <item x="60"/>
-        <item x="77"/>
-        <item x="71"/>
-        <item x="40"/>
-        <item x="45"/>
-        <item x="8"/>
-        <item x="62"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item x="59"/>
-        <item x="6"/>
-        <item x="36"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="65"/>
-        <item x="55"/>
-        <item x="39"/>
-        <item x="79"/>
-        <item x="20"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="2"/>
-        <item x="24"/>
-        <item x="67"/>
-        <item x="35"/>
-        <item x="51"/>
-        <item x="46"/>
-        <item x="69"/>
-        <item x="5"/>
-        <item x="22"/>
-        <item x="68"/>
-        <item x="21"/>
-        <item x="70"/>
-        <item x="32"/>
-        <item x="56"/>
-        <item x="17"/>
-        <item x="37"/>
-        <item x="66"/>
-        <item x="44"/>
-        <item x="75"/>
-        <item x="42"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="38"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="33">
-        <item x="19"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="18"/>
-        <item x="15"/>
-        <item x="30"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="29"/>
-        <item x="3"/>
-        <item x="31"/>
-        <item x="11"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="25"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="28"/>
-        <item x="26"/>
-        <item x="4"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="23"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable22.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1683D31-7513-458E-BE01-D7FE93FC7DB4}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="BD25:BE27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="23">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="82">
-        <item x="52"/>
-        <item x="25"/>
-        <item x="63"/>
-        <item x="49"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="48"/>
-        <item x="15"/>
-        <item x="28"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="1"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="50"/>
-        <item x="61"/>
-        <item x="29"/>
-        <item x="80"/>
-        <item x="7"/>
-        <item x="54"/>
-        <item x="19"/>
-        <item x="57"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="53"/>
-        <item x="47"/>
-        <item x="58"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="23"/>
-        <item x="76"/>
-        <item x="43"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="16"/>
-        <item x="60"/>
-        <item x="77"/>
-        <item x="71"/>
-        <item x="40"/>
-        <item x="45"/>
-        <item x="8"/>
-        <item x="62"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item x="59"/>
-        <item x="6"/>
-        <item x="36"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="65"/>
-        <item x="55"/>
-        <item x="39"/>
-        <item x="79"/>
-        <item x="20"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="2"/>
-        <item x="24"/>
-        <item x="67"/>
-        <item x="35"/>
-        <item x="51"/>
-        <item x="46"/>
-        <item x="69"/>
-        <item x="5"/>
-        <item x="22"/>
-        <item x="68"/>
-        <item x="21"/>
-        <item x="70"/>
-        <item x="32"/>
-        <item x="56"/>
-        <item x="17"/>
-        <item x="37"/>
-        <item x="66"/>
-        <item x="44"/>
-        <item x="75"/>
-        <item x="42"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="38"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="33">
-        <item x="19"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="18"/>
-        <item x="15"/>
-        <item x="30"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="29"/>
-        <item x="3"/>
-        <item x="31"/>
-        <item x="11"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="25"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="28"/>
-        <item x="26"/>
-        <item x="4"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="23"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="23">
-        <item x="15"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="19"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="18"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="12"/>
-        <item x="20"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="8"/>
-        <item x="13"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="18"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="16"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="18" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="1" filterVal="1"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable23.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{03411E7A-FBFF-49F0-9C83-B376FC4609A6}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="BP41:BS48" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="23">
-    <pivotField dataField="1" showAll="0">
-      <items count="101">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="82">
-        <item x="52"/>
-        <item x="25"/>
-        <item x="63"/>
-        <item x="49"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="48"/>
-        <item x="15"/>
-        <item x="28"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="1"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="50"/>
-        <item x="61"/>
-        <item x="29"/>
-        <item x="80"/>
-        <item x="7"/>
-        <item x="54"/>
-        <item x="19"/>
-        <item x="57"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="53"/>
-        <item x="47"/>
-        <item x="58"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="23"/>
-        <item x="76"/>
-        <item x="43"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="16"/>
-        <item x="60"/>
-        <item x="77"/>
-        <item x="71"/>
-        <item x="40"/>
-        <item x="45"/>
-        <item x="8"/>
-        <item x="62"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item x="59"/>
-        <item x="6"/>
-        <item x="36"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="65"/>
-        <item x="55"/>
-        <item x="39"/>
-        <item x="79"/>
-        <item x="20"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="2"/>
-        <item x="24"/>
-        <item x="67"/>
-        <item x="35"/>
-        <item x="51"/>
-        <item x="46"/>
-        <item x="69"/>
-        <item x="5"/>
-        <item x="22"/>
-        <item x="68"/>
-        <item x="21"/>
-        <item x="70"/>
-        <item x="32"/>
-        <item x="56"/>
-        <item x="17"/>
-        <item x="37"/>
-        <item x="66"/>
-        <item x="44"/>
-        <item x="75"/>
-        <item x="42"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="38"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="33">
-        <item x="19"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="18"/>
-        <item x="15"/>
-        <item x="30"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="29"/>
-        <item x="3"/>
-        <item x="31"/>
-        <item x="11"/>
-        <item x="13"/>
-        <item x="22"/>
-        <item x="25"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="28"/>
-        <item x="26"/>
-        <item x="4"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="23"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable24.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{839F4447-4F37-46E9-85EE-A9A4A65BA018}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="AE110:AE111" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="23">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -23461,7 +20110,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C9EA5E1-62FC-4589-8CD2-207FA1A68382}" name="PivotTable19" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="CJ37:CK39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
@@ -23474,11 +20123,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -23752,20 +20401,666 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E30E125-2571-4287-88E1-5AFA8E91D3A7}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="82">
+        <item x="52"/>
+        <item x="25"/>
+        <item x="63"/>
+        <item x="49"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="48"/>
+        <item x="15"/>
+        <item x="28"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="50"/>
+        <item x="61"/>
+        <item x="29"/>
+        <item x="80"/>
+        <item x="7"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="57"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="53"/>
+        <item x="47"/>
+        <item x="58"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="23"/>
+        <item x="76"/>
+        <item x="43"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="16"/>
+        <item x="60"/>
+        <item x="77"/>
+        <item x="71"/>
+        <item x="40"/>
+        <item x="45"/>
+        <item x="8"/>
+        <item x="62"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item x="59"/>
+        <item x="6"/>
+        <item x="36"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="65"/>
+        <item x="55"/>
+        <item x="39"/>
+        <item x="79"/>
+        <item x="20"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="2"/>
+        <item x="24"/>
+        <item x="67"/>
+        <item x="35"/>
+        <item x="51"/>
+        <item x="46"/>
+        <item x="69"/>
+        <item x="5"/>
+        <item x="22"/>
+        <item x="68"/>
+        <item x="21"/>
+        <item x="70"/>
+        <item x="32"/>
+        <item x="56"/>
+        <item x="17"/>
+        <item x="37"/>
+        <item x="66"/>
+        <item x="44"/>
+        <item x="75"/>
+        <item x="42"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="38"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="33">
+        <item x="19"/>
+        <item x="24"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="18"/>
+        <item x="15"/>
+        <item x="30"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="29"/>
+        <item x="3"/>
+        <item x="31"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="28"/>
+        <item x="26"/>
+        <item x="4"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="13" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="33" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="33" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="33" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="33" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{22C8BE52-12B2-49F3-829B-86C223E7AEBF}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="BP34:BR36" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="82">
+        <item x="52"/>
+        <item x="25"/>
+        <item x="63"/>
+        <item x="49"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="48"/>
+        <item x="15"/>
+        <item x="28"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="50"/>
+        <item x="61"/>
+        <item x="29"/>
+        <item x="80"/>
+        <item x="7"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="57"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="53"/>
+        <item x="47"/>
+        <item x="58"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="23"/>
+        <item x="76"/>
+        <item x="43"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="16"/>
+        <item x="60"/>
+        <item x="77"/>
+        <item x="71"/>
+        <item x="40"/>
+        <item x="45"/>
+        <item x="8"/>
+        <item x="62"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item x="59"/>
+        <item x="6"/>
+        <item x="36"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="65"/>
+        <item x="55"/>
+        <item x="39"/>
+        <item x="79"/>
+        <item x="20"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="2"/>
+        <item x="24"/>
+        <item x="67"/>
+        <item x="35"/>
+        <item x="51"/>
+        <item x="46"/>
+        <item x="69"/>
+        <item x="5"/>
+        <item x="22"/>
+        <item x="68"/>
+        <item x="21"/>
+        <item x="70"/>
+        <item x="32"/>
+        <item x="56"/>
+        <item x="17"/>
+        <item x="37"/>
+        <item x="66"/>
+        <item x="44"/>
+        <item x="75"/>
+        <item x="42"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="38"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="33">
+        <item x="19"/>
+        <item x="24"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="18"/>
+        <item x="15"/>
+        <item x="30"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="29"/>
+        <item x="3"/>
+        <item x="31"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="28"/>
+        <item x="26"/>
+        <item x="4"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable21.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{27782670-B934-4CA8-8981-727E61598DA9}" name="PivotTable16" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="BZ37:CA43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="BZ37:CA39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -23783,11 +21078,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24007,21 +21302,9 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="2">
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -24045,7 +21328,279 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable22.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1D668290-96DF-4F7E-8FE1-3AAB3593B7DF}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="">
+  <location ref="CF24:CG26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="82">
+        <item x="52"/>
+        <item x="25"/>
+        <item x="63"/>
+        <item x="49"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="48"/>
+        <item x="15"/>
+        <item x="28"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="50"/>
+        <item x="61"/>
+        <item x="29"/>
+        <item x="80"/>
+        <item x="7"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="57"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="53"/>
+        <item x="47"/>
+        <item x="58"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="23"/>
+        <item x="76"/>
+        <item x="43"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="16"/>
+        <item x="60"/>
+        <item x="77"/>
+        <item x="71"/>
+        <item x="40"/>
+        <item x="45"/>
+        <item x="8"/>
+        <item x="62"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item x="59"/>
+        <item x="6"/>
+        <item x="36"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="65"/>
+        <item x="55"/>
+        <item x="39"/>
+        <item x="79"/>
+        <item x="20"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="2"/>
+        <item x="24"/>
+        <item x="67"/>
+        <item x="35"/>
+        <item x="51"/>
+        <item x="46"/>
+        <item x="69"/>
+        <item x="5"/>
+        <item x="22"/>
+        <item x="68"/>
+        <item x="21"/>
+        <item x="70"/>
+        <item x="32"/>
+        <item x="56"/>
+        <item x="17"/>
+        <item x="37"/>
+        <item x="66"/>
+        <item x="44"/>
+        <item x="75"/>
+        <item x="42"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="38"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="33">
+        <item x="19"/>
+        <item x="24"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="18"/>
+        <item x="15"/>
+        <item x="30"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="29"/>
+        <item x="3"/>
+        <item x="31"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="28"/>
+        <item x="26"/>
+        <item x="4"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable23.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F07325B4-6664-4856-9B4A-CC3EAF737C6E}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BA25:BA26" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="23">
@@ -24054,11 +21609,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24067,11 +21622,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24309,20 +21864,1306 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable24.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1683D31-7513-458E-BE01-D7FE93FC7DB4}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="BD25:BE27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="82">
+        <item x="52"/>
+        <item x="25"/>
+        <item x="63"/>
+        <item x="49"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="48"/>
+        <item x="15"/>
+        <item x="28"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="50"/>
+        <item x="61"/>
+        <item x="29"/>
+        <item x="80"/>
+        <item x="7"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="57"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="53"/>
+        <item x="47"/>
+        <item x="58"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="23"/>
+        <item x="76"/>
+        <item x="43"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="16"/>
+        <item x="60"/>
+        <item x="77"/>
+        <item x="71"/>
+        <item x="40"/>
+        <item x="45"/>
+        <item x="8"/>
+        <item x="62"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item x="59"/>
+        <item x="6"/>
+        <item x="36"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="65"/>
+        <item x="55"/>
+        <item x="39"/>
+        <item x="79"/>
+        <item x="20"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="2"/>
+        <item x="24"/>
+        <item x="67"/>
+        <item x="35"/>
+        <item x="51"/>
+        <item x="46"/>
+        <item x="69"/>
+        <item x="5"/>
+        <item x="22"/>
+        <item x="68"/>
+        <item x="21"/>
+        <item x="70"/>
+        <item x="32"/>
+        <item x="56"/>
+        <item x="17"/>
+        <item x="37"/>
+        <item x="66"/>
+        <item x="44"/>
+        <item x="75"/>
+        <item x="42"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="38"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="33">
+        <item x="19"/>
+        <item x="24"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="18"/>
+        <item x="15"/>
+        <item x="30"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="29"/>
+        <item x="3"/>
+        <item x="31"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="28"/>
+        <item x="26"/>
+        <item x="4"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="23">
+        <item x="15"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="19"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="18"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="18" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="1" filterVal="1"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable25.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7AD66EF4-25E2-4CDC-BCB8-079B388A220D}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="X109:Z111" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="82">
+        <item x="52"/>
+        <item x="25"/>
+        <item x="63"/>
+        <item x="49"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="48"/>
+        <item x="15"/>
+        <item x="28"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="50"/>
+        <item x="61"/>
+        <item x="29"/>
+        <item x="80"/>
+        <item x="7"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="57"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="53"/>
+        <item x="47"/>
+        <item x="58"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="23"/>
+        <item x="76"/>
+        <item x="43"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="16"/>
+        <item x="60"/>
+        <item x="77"/>
+        <item x="71"/>
+        <item x="40"/>
+        <item x="45"/>
+        <item x="8"/>
+        <item x="62"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item x="59"/>
+        <item x="6"/>
+        <item x="36"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="65"/>
+        <item x="55"/>
+        <item x="39"/>
+        <item x="79"/>
+        <item x="20"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="2"/>
+        <item x="24"/>
+        <item x="67"/>
+        <item x="35"/>
+        <item x="51"/>
+        <item x="46"/>
+        <item x="69"/>
+        <item x="5"/>
+        <item x="22"/>
+        <item x="68"/>
+        <item x="21"/>
+        <item x="70"/>
+        <item x="32"/>
+        <item x="56"/>
+        <item x="17"/>
+        <item x="37"/>
+        <item x="66"/>
+        <item x="44"/>
+        <item x="75"/>
+        <item x="42"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="38"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="33">
+        <item x="19"/>
+        <item x="24"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="18"/>
+        <item x="15"/>
+        <item x="30"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="29"/>
+        <item x="3"/>
+        <item x="31"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="28"/>
+        <item x="26"/>
+        <item x="4"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable26.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2990033C-D272-4515-AFC8-96BC4B8D49ED}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="CM36:CN40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="82">
+        <item x="52"/>
+        <item x="25"/>
+        <item x="63"/>
+        <item x="49"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="48"/>
+        <item x="15"/>
+        <item x="28"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="50"/>
+        <item x="61"/>
+        <item x="29"/>
+        <item x="80"/>
+        <item x="7"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="57"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="53"/>
+        <item x="47"/>
+        <item x="58"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="23"/>
+        <item x="76"/>
+        <item x="43"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="16"/>
+        <item x="60"/>
+        <item x="77"/>
+        <item x="71"/>
+        <item x="40"/>
+        <item x="45"/>
+        <item x="8"/>
+        <item x="62"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item x="59"/>
+        <item x="6"/>
+        <item x="36"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="65"/>
+        <item x="55"/>
+        <item x="39"/>
+        <item x="79"/>
+        <item x="20"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="2"/>
+        <item x="24"/>
+        <item x="67"/>
+        <item x="35"/>
+        <item x="51"/>
+        <item x="46"/>
+        <item x="69"/>
+        <item x="5"/>
+        <item x="22"/>
+        <item x="68"/>
+        <item x="21"/>
+        <item x="70"/>
+        <item x="32"/>
+        <item x="56"/>
+        <item x="17"/>
+        <item x="37"/>
+        <item x="66"/>
+        <item x="44"/>
+        <item x="75"/>
+        <item x="42"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="38"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="33">
+        <item x="19"/>
+        <item x="24"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="18"/>
+        <item x="15"/>
+        <item x="30"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="29"/>
+        <item x="3"/>
+        <item x="31"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="28"/>
+        <item x="26"/>
+        <item x="4"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="23">
+        <item x="15"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="19"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="18"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Total Amount" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="18" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="1" filterVal="1"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable27.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{03411E7A-FBFF-49F0-9C83-B376FC4609A6}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="BP41:BS44" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField dataField="1" showAll="0">
+      <items count="101">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="82">
+        <item x="52"/>
+        <item x="25"/>
+        <item x="63"/>
+        <item x="49"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="48"/>
+        <item x="15"/>
+        <item x="28"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="50"/>
+        <item x="61"/>
+        <item x="29"/>
+        <item x="80"/>
+        <item x="7"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="57"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="53"/>
+        <item x="47"/>
+        <item x="58"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="23"/>
+        <item x="76"/>
+        <item x="43"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="16"/>
+        <item x="60"/>
+        <item x="77"/>
+        <item x="71"/>
+        <item x="40"/>
+        <item x="45"/>
+        <item x="8"/>
+        <item x="62"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item x="59"/>
+        <item x="6"/>
+        <item x="36"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="65"/>
+        <item x="55"/>
+        <item x="39"/>
+        <item x="79"/>
+        <item x="20"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="2"/>
+        <item x="24"/>
+        <item x="67"/>
+        <item x="35"/>
+        <item x="51"/>
+        <item x="46"/>
+        <item x="69"/>
+        <item x="5"/>
+        <item x="22"/>
+        <item x="68"/>
+        <item x="21"/>
+        <item x="70"/>
+        <item x="32"/>
+        <item x="56"/>
+        <item x="17"/>
+        <item x="37"/>
+        <item x="66"/>
+        <item x="44"/>
+        <item x="75"/>
+        <item x="42"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="38"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="33">
+        <item x="19"/>
+        <item x="24"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="18"/>
+        <item x="15"/>
+        <item x="30"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="29"/>
+        <item x="3"/>
+        <item x="31"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="28"/>
+        <item x="26"/>
+        <item x="4"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1B3412A-555A-468A-BFD1-ADB8628A4CEA}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
-  <location ref="A4:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <location ref="A4:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24555,21 +23396,9 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -24580,16 +23409,16 @@
   </colItems>
   <pageFields count="2">
     <pageField fld="14" hier="-1"/>
-    <pageField fld="7" hier="-1"/>
+    <pageField fld="7" item="1" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Average of Average Delivery Time " fld="15" subtotal="average" baseField="0" baseItem="0" numFmtId="1"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="21">
+    <format dxfId="41">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="40">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -24634,11 +23463,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24647,11 +23476,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24901,11 +23730,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24914,11 +23743,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -25158,18 +23987,18 @@
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7D1741C0-FAC1-4DC9-8406-C2DC3348114B}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:E5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <location ref="A3:C5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -25178,11 +24007,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -25412,15 +24241,9 @@
   <colFields count="1">
     <field x="17"/>
   </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
+  <colItems count="2">
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -25443,18 +24266,18 @@
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5819D107-A40B-4FBE-A2A4-9A3F023DF9CA}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -25472,11 +24295,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -25696,15 +24519,9 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="2">
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -25717,15 +24534,6 @@
     <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="3" type="count" evalOrder="-1" id="2" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="3" filterVal="3"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -25739,18 +24547,18 @@
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A88B0652-E428-4537-AF13-29F52E9B9B1F}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -25759,11 +24567,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -26009,12 +24817,15 @@
   <rowFields count="1">
     <field x="18"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="4">
+    <i>
+      <x v="10"/>
+    </i>
     <i>
       <x v="11"/>
     </i>
     <i>
-      <x v="19"/>
+      <x v="21"/>
     </i>
     <i t="grand">
       <x/>
@@ -26056,11 +24867,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -26069,11 +24880,11 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -26321,7 +25132,7 @@
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="16"/>
+      <x v="11"/>
     </i>
     <i t="grand">
       <x/>
@@ -26382,11 +25193,11 @@
   <data>
     <tabular pivotCacheId="59243591">
       <items count="5">
-        <i x="3" s="1"/>
-        <i x="1" s="1"/>
+        <i x="3"/>
+        <i x="1"/>
         <i x="0" s="1"/>
-        <i x="2" s="1"/>
-        <i x="4" s="1"/>
+        <i x="2"/>
+        <i x="4"/>
       </items>
     </tabular>
   </data>
@@ -26422,11 +25233,11 @@
   <data>
     <tabular pivotCacheId="59243591">
       <items count="5">
-        <i x="3" s="1"/>
+        <i x="3"/>
         <i x="0" s="1"/>
-        <i x="1" s="1"/>
-        <i x="4" s="1"/>
-        <i x="2" s="1"/>
+        <i x="1"/>
+        <i x="4"/>
+        <i x="2"/>
       </items>
     </tabular>
   </data>
@@ -26462,8 +25273,8 @@
     <tabular pivotCacheId="59243591">
       <items count="3">
         <i x="0" s="1"/>
-        <i x="1" s="1"/>
         <i x="2" s="1"/>
+        <i x="1" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -26562,22 +25373,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D5482C80-47D9-46AB-AD05-3809B0FAE5D0}" name="Table1" displayName="Table1" ref="A1:S101" totalsRowShown="0" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D5482C80-47D9-46AB-AD05-3809B0FAE5D0}" name="Table1" displayName="Table1" ref="A1:S101" totalsRowShown="0" tableBorderDxfId="34">
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{47016FAD-65CB-4ACF-B9AA-E3806242A9F4}" name="Order ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{BBD3FD06-E866-4001-AE8D-D0B0A5D87E93}" name="Customer ID" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{1DA0EFA9-3E51-4AE3-984D-869D4753159E}" name="Product ID" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{5FFB34AE-D274-44D1-8F71-310935EB018F}" name="Region" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{2A061E60-0259-4D62-80B0-5843E6A778B9}" name="Sale Price/Unit" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{8D09C0F2-5918-4C73-B6FB-C888162CA8E8}" name="Quantity" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{4D1BAA63-ED10-4E65-B8E9-E0F5215B6016}" name="Total Amount" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{564673C0-EFA8-459B-899E-0CF2960C6532}" name="Payment Method" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{802A48C2-E61F-48C8-9F3D-B4717993373D}" name="Delivery Status" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{249039DD-FF0A-4E41-B091-4329AF09912A}" name="Fulfillment Partner" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{50674A37-EF11-4500-8938-8D7A587B3BC5}" name="Order Date" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{796408B9-677F-480D-91CD-A0F614A8829D}" name="Delivery Date" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{9187AB19-2C53-47B2-85E9-4169B20FBC04}" name="Cancel Date" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{EDC60799-CEF2-4F16-9CBA-7D311429DB2B}" name="is cancel" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{47016FAD-65CB-4ACF-B9AA-E3806242A9F4}" name="Order ID" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{BBD3FD06-E866-4001-AE8D-D0B0A5D87E93}" name="Customer ID" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{1DA0EFA9-3E51-4AE3-984D-869D4753159E}" name="Product ID" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{5FFB34AE-D274-44D1-8F71-310935EB018F}" name="Region" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{2A061E60-0259-4D62-80B0-5843E6A778B9}" name="Sale Price/Unit" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{8D09C0F2-5918-4C73-B6FB-C888162CA8E8}" name="Quantity" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{4D1BAA63-ED10-4E65-B8E9-E0F5215B6016}" name="Total Amount" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{564673C0-EFA8-459B-899E-0CF2960C6532}" name="Payment Method" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{802A48C2-E61F-48C8-9F3D-B4717993373D}" name="Delivery Status" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{249039DD-FF0A-4E41-B091-4329AF09912A}" name="Fulfillment Partner" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{50674A37-EF11-4500-8938-8D7A587B3BC5}" name="Order Date" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{796408B9-677F-480D-91CD-A0F614A8829D}" name="Delivery Date" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{9187AB19-2C53-47B2-85E9-4169B20FBC04}" name="Cancel Date" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{EDC60799-CEF2-4F16-9CBA-7D311429DB2B}" name="is cancel" dataDxfId="20">
       <calculatedColumnFormula>IF(OR(I2="cancelled",M2&lt;&gt;""),"YES","NO")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{0D57CD57-0419-4015-B33A-3E7A12154B5C}" name="Product Category">
@@ -26863,21 +25674,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE70153-D943-4572-B81C-6E6A4299CA8F}">
-  <dimension ref="A2:I10"/>
+  <dimension ref="A2:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -26893,160 +25703,41 @@
         <v>311</v>
       </c>
       <c r="B4" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="C4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E4" t="s">
-        <v>206</v>
-      </c>
-      <c r="F4" t="s">
-        <v>203</v>
-      </c>
-      <c r="G4" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5">
-        <v>84</v>
-      </c>
-      <c r="C5">
-        <v>2662</v>
-      </c>
-      <c r="D5">
-        <v>210</v>
-      </c>
-      <c r="E5">
-        <v>2063</v>
-      </c>
-      <c r="F5">
-        <v>437</v>
-      </c>
-      <c r="G5">
-        <v>5456</v>
+        <v>12</v>
+      </c>
+      <c r="B5" s="32">
+        <v>81</v>
+      </c>
+      <c r="C5" s="32">
+        <v>64</v>
+      </c>
+      <c r="D5" s="32">
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6">
-        <v>394</v>
-      </c>
-      <c r="C6">
-        <v>365</v>
-      </c>
-      <c r="D6">
-        <v>711</v>
-      </c>
-      <c r="E6">
-        <v>741</v>
-      </c>
-      <c r="F6">
-        <v>1424</v>
-      </c>
-      <c r="G6">
-        <v>3635</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>464</v>
-      </c>
-      <c r="C7">
-        <v>6522</v>
-      </c>
-      <c r="D7">
-        <v>788</v>
-      </c>
-      <c r="E7">
-        <v>2131</v>
-      </c>
-      <c r="F7">
-        <v>586</v>
-      </c>
-      <c r="G7">
-        <v>10491</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8">
-        <v>423</v>
-      </c>
-      <c r="C8">
-        <v>3938</v>
-      </c>
-      <c r="D8">
-        <v>1032</v>
-      </c>
-      <c r="E8">
-        <v>1881</v>
-      </c>
-      <c r="F8">
-        <v>43</v>
-      </c>
-      <c r="G8">
-        <v>7317</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9">
-        <v>350</v>
-      </c>
-      <c r="C9">
-        <v>1722</v>
-      </c>
-      <c r="D9">
-        <v>1131</v>
-      </c>
-      <c r="E9">
-        <v>4135</v>
-      </c>
-      <c r="F9">
-        <v>1021</v>
-      </c>
-      <c r="G9">
-        <v>8359</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B10">
-        <v>1715</v>
-      </c>
-      <c r="C10">
-        <v>15209</v>
-      </c>
-      <c r="D10">
-        <v>3872</v>
-      </c>
-      <c r="E10">
-        <v>10951</v>
-      </c>
-      <c r="F10">
-        <v>3511</v>
-      </c>
-      <c r="G10">
-        <v>35258</v>
+      <c r="B6" s="32">
+        <v>81</v>
+      </c>
+      <c r="C6" s="32">
+        <v>64</v>
+      </c>
+      <c r="D6" s="32">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -27057,7 +25748,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6182FA78-8D02-460E-9599-0F18B7DDC883}">
-  <dimension ref="A3:B16"/>
+  <dimension ref="A3:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -27074,106 +25765,34 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="B4">
-        <v>1099</v>
+        <v>343</v>
+      </c>
+      <c r="B4" s="32">
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="B5">
-        <v>3712</v>
+        <v>344</v>
+      </c>
+      <c r="B5" s="32">
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="B6">
-        <v>905</v>
+        <v>345</v>
+      </c>
+      <c r="B6" s="32">
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="B7">
-        <v>2637</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="B8">
-        <v>4940</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="B9">
-        <v>2599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="B10">
-        <v>3315</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="B11">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="B12">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="B13">
-        <v>2920</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="B14">
-        <v>6312</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="B15">
-        <v>4467</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B16">
-        <v>35258</v>
+      <c r="B7" s="32">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -27199,73 +25818,61 @@
         <v>313</v>
       </c>
       <c r="C3" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="D3" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="G3" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B4">
-        <v>10491</v>
-      </c>
-      <c r="C4" t="e">
+      <c r="B4" s="32">
+        <v>145</v>
+      </c>
+      <c r="C4">
         <f>IF(B4&lt;6000,B4,NA())</f>
+        <v>145</v>
+      </c>
+      <c r="D4" t="e">
+        <f>IF(B4&gt;=6000,B4,NA())</f>
         <v>#N/A</v>
-      </c>
-      <c r="D4">
-        <f>IF(B4&gt;=6000,B4,NA())</f>
-        <v>10491</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5">
-        <v>8359</v>
-      </c>
-      <c r="C5" t="e">
+        <v>312</v>
+      </c>
+      <c r="B5" s="32">
+        <v>145</v>
+      </c>
+      <c r="C5">
         <f>IF(B5&lt;6000,B5,NA())</f>
+        <v>145</v>
+      </c>
+      <c r="D5" t="e">
+        <f t="shared" ref="D5:D8" si="0">IF(B5&gt;=6000,B5,NA())</f>
         <v>#N/A</v>
-      </c>
-      <c r="D5">
-        <f t="shared" ref="D5:D8" si="0">IF(B5&gt;=6000,B5,NA())</f>
-        <v>8359</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
-        <v>7317</v>
-      </c>
-      <c r="C6" t="e">
+      <c r="C6">
         <f t="shared" ref="C6:C8" si="1">IF(B6&lt;6000,B6,NA())</f>
+        <v>0</v>
+      </c>
+      <c r="D6" t="e">
+        <f t="shared" si="0"/>
         <v>#N/A</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>7317</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>5456</v>
-      </c>
       <c r="C7">
         <f t="shared" si="1"/>
-        <v>5456</v>
+        <v>0</v>
       </c>
       <c r="D7" t="e">
         <f t="shared" si="0"/>
@@ -27273,27 +25880,13 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>3635</v>
-      </c>
       <c r="C8">
         <f t="shared" si="1"/>
-        <v>3635</v>
+        <v>0</v>
       </c>
       <c r="D8" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="B9">
-        <v>35258</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -27355,12 +25948,12 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -27379,13 +25972,13 @@
         <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D4" t="s">
         <v>312</v>
       </c>
       <c r="E4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -27511,13 +26104,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" s="18" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -27545,10 +26138,10 @@
         <v>9644</v>
       </c>
       <c r="C5" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="D5" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -27607,13 +26200,13 @@
         <v>322</v>
       </c>
       <c r="C15" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D15" t="s">
         <v>312</v>
       </c>
       <c r="E15" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -27722,12 +26315,12 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -27772,107 +26365,107 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -27880,23 +26473,23 @@
     </row>
     <row r="61" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="G61" s="19"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -27929,7 +26522,7 @@
         <v>319</v>
       </c>
       <c r="F3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -27956,7 +26549,7 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -28046,7 +26639,7 @@
         <v>320</v>
       </c>
       <c r="S1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -35629,14 +34222,14 @@
   <cols>
     <col min="24" max="24" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="5" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="19.21875" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="26.21875" bestFit="1" customWidth="1"/>
@@ -35644,19 +34237,19 @@
     <col min="69" max="69" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="4" bestFit="1" customWidth="1"/>
     <col min="71" max="72" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="79" max="79" width="19.21875" bestFit="1" customWidth="1"/>
     <col min="84" max="84" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="85" max="85" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="89" max="89" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="92" max="92" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -35931,11 +34524,11 @@
         <v>311</v>
       </c>
       <c r="BH24" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="CA24" s="19"/>
       <c r="CF24" s="9" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="CG24" t="s">
         <v>313</v>
@@ -35952,83 +34545,61 @@
         <v>313</v>
       </c>
       <c r="BG25" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="BH25">
-        <v>8</v>
+        <v>226</v>
+      </c>
+      <c r="BH25" s="32">
+        <v>1</v>
       </c>
       <c r="CF25" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="CG25">
-        <v>5456</v>
+        <v>12</v>
+      </c>
+      <c r="CG25" s="32">
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="53:85" x14ac:dyDescent="0.3">
-      <c r="BA26">
-        <v>35258</v>
+      <c r="BA26" s="32">
+        <v>145</v>
       </c>
       <c r="BD26" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="BE26">
-        <v>9644</v>
+        <v>208</v>
+      </c>
+      <c r="BE26" s="32">
+        <v>64</v>
       </c>
       <c r="BG26" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="BH26">
-        <v>8</v>
+        <v>208</v>
+      </c>
+      <c r="BH26" s="32">
+        <v>1</v>
       </c>
       <c r="CF26" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="CG26">
-        <v>3635</v>
+        <v>312</v>
+      </c>
+      <c r="CG26" s="32">
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="53:85" x14ac:dyDescent="0.3">
       <c r="BD27" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="BE27">
-        <v>9644</v>
+      <c r="BE27" s="32">
+        <v>64</v>
       </c>
       <c r="BG27" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="BH27">
-        <v>16</v>
-      </c>
-      <c r="CF27" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="CG27">
-        <v>10491</v>
+        <v>244</v>
+      </c>
+      <c r="BH27" s="32">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="53:85" x14ac:dyDescent="0.3">
-      <c r="CF28" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="CG28">
-        <v>7317</v>
-      </c>
-    </row>
-    <row r="29" spans="53:85" x14ac:dyDescent="0.3">
-      <c r="CF29" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="CG29">
-        <v>8359</v>
-      </c>
-    </row>
-    <row r="30" spans="53:85" x14ac:dyDescent="0.3">
-      <c r="CF30" s="10" t="s">
+      <c r="BG28" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="CG30">
-        <v>35258</v>
+      <c r="BH28" s="32">
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="61:95" x14ac:dyDescent="0.3">
@@ -36036,7 +34607,7 @@
         <v>321</v>
       </c>
       <c r="BU34" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35" spans="61:95" x14ac:dyDescent="0.3">
@@ -36044,12 +34615,6 @@
         <v>323</v>
       </c>
       <c r="BR35" t="s">
-        <v>324</v>
-      </c>
-      <c r="BS35" t="s">
-        <v>325</v>
-      </c>
-      <c r="BT35" t="s">
         <v>312</v>
       </c>
       <c r="CQ35" s="19"/>
@@ -36058,27 +34623,21 @@
       <c r="BP36" t="s">
         <v>319</v>
       </c>
-      <c r="BQ36">
-        <v>11</v>
-      </c>
-      <c r="BR36">
-        <v>66</v>
-      </c>
-      <c r="BS36">
-        <v>23</v>
-      </c>
-      <c r="BT36">
-        <v>100</v>
+      <c r="BQ36" s="32">
+        <v>3</v>
+      </c>
+      <c r="BR36" s="32">
+        <v>3</v>
       </c>
       <c r="BU36" s="15">
         <f>BQ36/(BQ36+BS36)</f>
-        <v>0.3235294117647059</v>
+        <v>1</v>
       </c>
       <c r="CM36" s="9" t="s">
         <v>311</v>
       </c>
       <c r="CN36" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" spans="61:95" x14ac:dyDescent="0.3">
@@ -36089,13 +34648,13 @@
         <v>322</v>
       </c>
       <c r="BK37" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="BL37" t="s">
         <v>312</v>
       </c>
       <c r="BM37" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="BZ37" s="9" t="s">
         <v>311</v>
@@ -36110,10 +34669,10 @@
         <v>313</v>
       </c>
       <c r="CM37" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="CN37">
-        <v>8</v>
+        <v>226</v>
+      </c>
+      <c r="CN37" s="32">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="61:95" x14ac:dyDescent="0.3">
@@ -36136,20 +34695,20 @@
       <c r="BZ38" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="CA38">
-        <v>10491</v>
+      <c r="CA38" s="32">
+        <v>145</v>
       </c>
       <c r="CJ38" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="CK38">
-        <v>9644</v>
+      <c r="CK38" s="32">
+        <v>1606</v>
       </c>
       <c r="CM38" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="CN38">
-        <v>8</v>
+        <v>208</v>
+      </c>
+      <c r="CN38" s="32">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="61:95" x14ac:dyDescent="0.3">
@@ -36170,22 +34729,22 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="BZ39" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="CA39">
-        <v>8359</v>
+        <v>312</v>
+      </c>
+      <c r="CA39" s="32">
+        <v>145</v>
       </c>
       <c r="CJ39" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="CK39">
-        <v>9644</v>
+      <c r="CK39" s="32">
+        <v>1606</v>
       </c>
       <c r="CM39" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="CN39">
-        <v>16</v>
+        <v>244</v>
+      </c>
+      <c r="CN39" s="32">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="61:95" x14ac:dyDescent="0.3">
@@ -36205,11 +34764,11 @@
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
-      <c r="BZ40" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="CA40">
-        <v>7317</v>
+      <c r="CM40" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="CN40" s="32">
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="61:95" x14ac:dyDescent="0.3">
@@ -36236,12 +34795,6 @@
         <v>321</v>
       </c>
       <c r="BT41" s="12"/>
-      <c r="BZ41" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="CA41">
-        <v>5456</v>
-      </c>
     </row>
     <row r="42" spans="61:95" x14ac:dyDescent="0.3">
       <c r="BI42" s="10" t="s">
@@ -36267,139 +34820,77 @@
         <v>322</v>
       </c>
       <c r="BR42" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="BS42" t="s">
         <v>312</v>
       </c>
       <c r="BT42" t="s">
-        <v>333</v>
-      </c>
-      <c r="BZ42" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="CA42">
-        <v>3635</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="61:95" x14ac:dyDescent="0.3">
       <c r="BP43" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="BQ43">
-        <v>9</v>
-      </c>
-      <c r="BR43">
-        <v>5</v>
-      </c>
-      <c r="BS43">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="BQ43" s="32">
+        <v>1</v>
+      </c>
+      <c r="BR43" s="32">
+        <v>2</v>
+      </c>
+      <c r="BS43" s="32">
+        <v>3</v>
       </c>
       <c r="BT43" s="15">
         <f>BR43/BS43</f>
-        <v>0.35714285714285715</v>
-      </c>
-      <c r="BZ43" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="CA43">
-        <v>35258</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="44" spans="61:95" x14ac:dyDescent="0.3">
       <c r="BP44" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="BQ44">
-        <v>15</v>
-      </c>
-      <c r="BR44">
+        <v>312</v>
+      </c>
+      <c r="BQ44" s="32">
+        <v>1</v>
+      </c>
+      <c r="BR44" s="32">
+        <v>2</v>
+      </c>
+      <c r="BS44" s="32">
         <v>3</v>
-      </c>
-      <c r="BS44">
-        <v>18</v>
       </c>
       <c r="BT44" s="15">
         <f t="shared" ref="BT44:BT47" si="1">BR44/BS44</f>
-        <v>0.16666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="45" spans="61:95" x14ac:dyDescent="0.3">
-      <c r="BP45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="BQ45">
-        <v>15</v>
-      </c>
-      <c r="BR45">
-        <v>10</v>
-      </c>
-      <c r="BS45">
-        <v>25</v>
-      </c>
-      <c r="BT45" s="15">
+      <c r="BT45" s="15" t="e">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="46" spans="61:95" x14ac:dyDescent="0.3">
-      <c r="BP46" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="BQ46">
-        <v>16</v>
-      </c>
-      <c r="BR46">
-        <v>4</v>
-      </c>
-      <c r="BS46">
-        <v>20</v>
-      </c>
-      <c r="BT46" s="15">
+      <c r="BT46" s="15" t="e">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="47" spans="61:95" x14ac:dyDescent="0.3">
-      <c r="BP47" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="BQ47">
-        <v>15</v>
-      </c>
-      <c r="BR47">
-        <v>8</v>
-      </c>
-      <c r="BS47">
-        <v>23</v>
-      </c>
-      <c r="BT47" s="15">
+      <c r="BT47" s="15" t="e">
         <f t="shared" si="1"/>
-        <v>0.34782608695652173</v>
-      </c>
-    </row>
-    <row r="48" spans="61:95" x14ac:dyDescent="0.3">
-      <c r="BP48" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="BQ48">
-        <v>70</v>
-      </c>
-      <c r="BR48">
-        <v>30</v>
-      </c>
-      <c r="BS48">
-        <v>100</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="97" spans="11:31" ht="72" x14ac:dyDescent="0.3">
       <c r="K97" s="19" t="str">
         <f>AV115&amp;CHAR(10)&amp;CM37&amp;"-"&amp;CN37</f>
         <v>Highest Selling Produsts by Units
-Leg Set-8</v>
+Lamp-1</v>
       </c>
       <c r="L97" s="19" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
     </row>
     <row r="109" spans="11:31" x14ac:dyDescent="0.3">
@@ -36407,7 +34898,7 @@
         <v>321</v>
       </c>
       <c r="AC109" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="110" spans="11:31" x14ac:dyDescent="0.3">
@@ -36415,12 +34906,6 @@
         <v>323</v>
       </c>
       <c r="Z110" t="s">
-        <v>324</v>
-      </c>
-      <c r="AA110" t="s">
-        <v>325</v>
-      </c>
-      <c r="AB110" t="s">
         <v>312</v>
       </c>
       <c r="AE110" t="s">
@@ -36431,24 +34916,18 @@
       <c r="X111" t="s">
         <v>319</v>
       </c>
-      <c r="Y111">
-        <v>11</v>
-      </c>
-      <c r="Z111">
-        <v>66</v>
-      </c>
-      <c r="AA111">
-        <v>23</v>
-      </c>
-      <c r="AB111">
-        <v>100</v>
+      <c r="Y111" s="32">
+        <v>3</v>
+      </c>
+      <c r="Z111" s="32">
+        <v>3</v>
       </c>
       <c r="AC111" s="15">
         <f>Y111/(Y111+AA111)</f>
-        <v>0.3235294117647059</v>
-      </c>
-      <c r="AE111">
-        <v>35258</v>
+        <v>1</v>
+      </c>
+      <c r="AE111" s="32">
+        <v>145</v>
       </c>
     </row>
     <row r="112" spans="11:31" hidden="1" x14ac:dyDescent="0.3"/>
@@ -36456,7 +34935,7 @@
     <row r="114" spans="5:49" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="115" spans="5:49" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AV115" s="19" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
     </row>
     <row r="116" spans="5:49" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -36465,37 +34944,37 @@
     <row r="119" spans="5:49" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="5:49" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E120" s="19" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="G120" s="19" t="str">
         <f>CF25&amp;"-"&amp;CG25&amp;CHAR(10)&amp;CF26&amp;"-"&amp;CG26&amp;CHAR(10)&amp;CF27&amp;"-"&amp;CG27</f>
-        <v>Central-5456
-East-3635
-North-10491</v>
+        <v>North-145
+Grand Total-145
+-</v>
       </c>
       <c r="M120" s="19" t="str">
         <f>BU34&amp;"-"&amp;BU36</f>
-        <v>% Fast Delivery -0.323529411764706</v>
+        <v>% Fast Delivery -1</v>
       </c>
       <c r="R120" s="24" t="str">
         <f>AC109&amp;"-"&amp;AD109&amp;"-"&amp;AC111</f>
-        <v>% Fast Delivery --0.323529411764706</v>
+        <v>% Fast Delivery --1</v>
       </c>
       <c r="U120" s="19" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="W120" s="19" t="str">
         <f>U120&amp;"-"&amp;AE111</f>
-        <v>Total Revnue-35258</v>
+        <v>Total Revnue-145</v>
       </c>
       <c r="X120" s="19" t="str">
         <f>L97&amp;CHAR(10)&amp;BD26&amp;"-"&amp;BE26</f>
         <v>Highest-Selling product by Revenue
-Smartphone-9644</v>
+Leg Set-64</v>
       </c>
       <c r="AV120" s="21"/>
       <c r="AW120" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
     </row>
     <row r="121" spans="5:49" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -36523,7 +35002,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CAD6665-C716-48F0-855F-9BD52FC1E5E4}">
-  <dimension ref="A3:D7"/>
+  <dimension ref="A3:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -36538,39 +35017,31 @@
         <v>319</v>
       </c>
       <c r="D3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B4">
-        <v>30</v>
+      <c r="B4" s="32">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
-        <v>34</v>
+        <v>22</v>
+      </c>
+      <c r="B5" s="32">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B7">
-        <v>100</v>
+      <c r="B6" s="32">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -36581,7 +35052,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DAC2CD-EF36-4E2E-A049-C47377CB0709}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
@@ -36601,10 +35072,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>318</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -36617,50 +35088,18 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="13">
-        <v>4.2</v>
+        <v>12</v>
+      </c>
+      <c r="B5" s="13" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="13">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="13">
-        <v>3.625</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="13">
-        <v>3.3333333333333335</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="13">
-        <v>3.4285714285714284</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B10" s="17">
-        <v>3.7647058823529411</v>
+      <c r="B6" s="17" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
@@ -36688,10 +35127,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -36701,8 +35140,8 @@
       <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>35258</v>
+      <c r="A4" s="32">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -36724,8 +35163,8 @@
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>35258</v>
+      <c r="A4" s="32">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -36740,14 +35179,14 @@
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -36755,10 +35194,10 @@
         <v>321</v>
       </c>
       <c r="F3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -36766,12 +35205,6 @@
         <v>323</v>
       </c>
       <c r="C4" t="s">
-        <v>324</v>
-      </c>
-      <c r="D4" t="s">
-        <v>325</v>
-      </c>
-      <c r="E4" t="s">
         <v>312</v>
       </c>
     </row>
@@ -36779,21 +35212,15 @@
       <c r="A5" t="s">
         <v>319</v>
       </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>66</v>
-      </c>
-      <c r="D5">
-        <v>23</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
+      <c r="B5" s="32">
+        <v>3</v>
+      </c>
+      <c r="C5" s="32">
+        <v>3</v>
       </c>
       <c r="F5" s="15">
         <f>B5/(B5+D5)</f>
-        <v>0.3235294117647059</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -36803,7 +35230,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3504FE4-12F6-4A3B-AC16-27163248EC33}">
-  <dimension ref="A2:E7"/>
+  <dimension ref="A2:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -36812,7 +35239,7 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -36827,32 +35254,16 @@
       <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B4">
-        <v>10491</v>
+      <c r="B4" s="32">
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5">
-        <v>8359</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
-        <v>7317</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B7">
-        <v>26167</v>
+      <c r="B5" s="32">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -36862,7 +35273,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A828A8-B879-450D-85A9-805EECC0263D}">
-  <dimension ref="A2:D6"/>
+  <dimension ref="A2:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -36871,7 +35282,7 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -36879,34 +35290,42 @@
         <v>311</v>
       </c>
       <c r="B3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
+        <v>226</v>
+      </c>
+      <c r="B4" s="32">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="B5">
-        <v>8</v>
+        <v>208</v>
+      </c>
+      <c r="B5" s="32">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B6">
-        <v>16</v>
+      <c r="B7" s="32">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -36925,7 +35344,7 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -36936,23 +35355,23 @@
         <v>313</v>
       </c>
       <c r="D3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B4">
-        <v>9644</v>
+        <v>208</v>
+      </c>
+      <c r="B4" s="32">
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B5">
-        <v>9644</v>
+      <c r="B5" s="32">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -36961,18 +35380,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37120,14 +35539,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9715FFF-A539-434C-BB0F-FF952CA2B3DB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2D1799E-4229-4117-9AB0-BB56F29486DD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -37139,6 +35550,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9715FFF-A539-434C-BB0F-FF952CA2B3DB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
